--- a/data/nzd0157/nzd0157.xlsx
+++ b/data/nzd0157/nzd0157.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q358"/>
+  <dimension ref="A1:Q360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20843,6 +20843,120 @@
         </is>
       </c>
     </row>
+    <row r="359">
+      <c r="A359" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>391.02</v>
+      </c>
+      <c r="C359" t="n">
+        <v>382.78</v>
+      </c>
+      <c r="D359" t="n">
+        <v>380.12</v>
+      </c>
+      <c r="E359" t="n">
+        <v>380.55</v>
+      </c>
+      <c r="F359" t="n">
+        <v>370.87</v>
+      </c>
+      <c r="G359" t="n">
+        <v>369.14</v>
+      </c>
+      <c r="H359" t="n">
+        <v>368.35</v>
+      </c>
+      <c r="I359" t="n">
+        <v>368.45</v>
+      </c>
+      <c r="J359" t="n">
+        <v>371.29</v>
+      </c>
+      <c r="K359" t="n">
+        <v>368.8</v>
+      </c>
+      <c r="L359" t="n">
+        <v>364.32</v>
+      </c>
+      <c r="M359" t="n">
+        <v>366.27</v>
+      </c>
+      <c r="N359" t="n">
+        <v>371.12</v>
+      </c>
+      <c r="O359" t="n">
+        <v>379.69</v>
+      </c>
+      <c r="P359" t="n">
+        <v>372.68</v>
+      </c>
+      <c r="Q359" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>391.45</v>
+      </c>
+      <c r="C360" t="n">
+        <v>383.13</v>
+      </c>
+      <c r="D360" t="n">
+        <v>379.55</v>
+      </c>
+      <c r="E360" t="n">
+        <v>380.26</v>
+      </c>
+      <c r="F360" t="n">
+        <v>371.12</v>
+      </c>
+      <c r="G360" t="n">
+        <v>368.87</v>
+      </c>
+      <c r="H360" t="n">
+        <v>366.07</v>
+      </c>
+      <c r="I360" t="n">
+        <v>366.28</v>
+      </c>
+      <c r="J360" t="n">
+        <v>370.13</v>
+      </c>
+      <c r="K360" t="n">
+        <v>368.64</v>
+      </c>
+      <c r="L360" t="n">
+        <v>364.69</v>
+      </c>
+      <c r="M360" t="n">
+        <v>365.36</v>
+      </c>
+      <c r="N360" t="n">
+        <v>371.12</v>
+      </c>
+      <c r="O360" t="n">
+        <v>379.69</v>
+      </c>
+      <c r="P360" t="n">
+        <v>372.68</v>
+      </c>
+      <c r="Q360" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20854,7 +20968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B374"/>
+  <dimension ref="A1:B376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24597,6 +24711,26 @@
       </c>
       <c r="B374" t="n">
         <v>-0.64</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>-0.34</v>
       </c>
     </row>
   </sheetData>
@@ -24765,28 +24899,28 @@
         <v>0.0555</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2720766313677508</v>
+        <v>0.2760193931334979</v>
       </c>
       <c r="J2" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K2" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2606175082596677</v>
+        <v>0.2674724578444523</v>
       </c>
       <c r="M2" t="n">
-        <v>2.57216886611112</v>
+        <v>2.577435497739846</v>
       </c>
       <c r="N2" t="n">
-        <v>11.62795742527552</v>
+        <v>11.63243887428726</v>
       </c>
       <c r="O2" t="n">
-        <v>3.409979094551097</v>
+        <v>3.410636139239608</v>
       </c>
       <c r="P2" t="n">
-        <v>380.3355946420447</v>
+        <v>380.2926960740504</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -24843,28 +24977,28 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3835547018523361</v>
+        <v>0.3909485631847673</v>
       </c>
       <c r="J3" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K3" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2917846897136858</v>
+        <v>0.299778877690698</v>
       </c>
       <c r="M3" t="n">
-        <v>3.555741708392964</v>
+        <v>3.572055825588657</v>
       </c>
       <c r="N3" t="n">
-        <v>19.77027944167622</v>
+        <v>19.90307211095878</v>
       </c>
       <c r="O3" t="n">
-        <v>4.446378238710268</v>
+        <v>4.461285925712314</v>
       </c>
       <c r="P3" t="n">
-        <v>365.9360991580734</v>
+        <v>365.8556538875935</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24921,28 +25055,28 @@
         <v>0.1281</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3413909215143846</v>
+        <v>0.3454323805376072</v>
       </c>
       <c r="J4" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K4" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2492881106624214</v>
+        <v>0.2553701391775827</v>
       </c>
       <c r="M4" t="n">
-        <v>3.344576025417965</v>
+        <v>3.345343770871169</v>
       </c>
       <c r="N4" t="n">
-        <v>19.43260570147169</v>
+        <v>19.39738215046525</v>
       </c>
       <c r="O4" t="n">
-        <v>4.408242926776119</v>
+        <v>4.404245923023061</v>
       </c>
       <c r="P4" t="n">
-        <v>366.9740486646427</v>
+        <v>366.9300817377563</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -24999,28 +25133,28 @@
         <v>0.09959999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2383782071599551</v>
+        <v>0.2456864306677493</v>
       </c>
       <c r="J5" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K5" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1560380550143488</v>
+        <v>0.1639753423273679</v>
       </c>
       <c r="M5" t="n">
-        <v>3.147625553015822</v>
+        <v>3.165878925742411</v>
       </c>
       <c r="N5" t="n">
-        <v>16.8475773787985</v>
+        <v>16.98734017670453</v>
       </c>
       <c r="O5" t="n">
-        <v>4.104580049018231</v>
+        <v>4.121570110613737</v>
       </c>
       <c r="P5" t="n">
-        <v>367.4423790041806</v>
+        <v>367.3623267175452</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25077,28 +25211,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1476914975886333</v>
+        <v>0.1515734590669267</v>
       </c>
       <c r="J6" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K6" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07712654969674582</v>
+        <v>0.08149161170638741</v>
       </c>
       <c r="M6" t="n">
-        <v>2.888000724369104</v>
+        <v>2.886628704795142</v>
       </c>
       <c r="N6" t="n">
-        <v>14.30741790677843</v>
+        <v>14.2935150963031</v>
       </c>
       <c r="O6" t="n">
-        <v>3.782514759624664</v>
+        <v>3.780676539497011</v>
       </c>
       <c r="P6" t="n">
-        <v>363.5386564289102</v>
+        <v>363.4961322217433</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25155,28 +25289,28 @@
         <v>0.1229</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2259755961332019</v>
+        <v>0.2276146257326646</v>
       </c>
       <c r="J7" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K7" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L7" t="n">
-        <v>0.178495268719702</v>
+        <v>0.182348951506448</v>
       </c>
       <c r="M7" t="n">
-        <v>2.856172086368829</v>
+        <v>2.846245620441249</v>
       </c>
       <c r="N7" t="n">
-        <v>12.88304331363298</v>
+        <v>12.8229384809846</v>
       </c>
       <c r="O7" t="n">
-        <v>3.589295657038158</v>
+        <v>3.580913079227782</v>
       </c>
       <c r="P7" t="n">
-        <v>361.4399926817476</v>
+        <v>361.4220403560958</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25233,28 +25367,28 @@
         <v>0.074</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2383390609678114</v>
+        <v>0.2396853756141315</v>
       </c>
       <c r="J8" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K8" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1533484846496634</v>
+        <v>0.1563460267995564</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2523369063811</v>
+        <v>3.240057250385952</v>
       </c>
       <c r="N8" t="n">
-        <v>17.19205035542765</v>
+        <v>17.11130298726151</v>
       </c>
       <c r="O8" t="n">
-        <v>4.146329745139386</v>
+        <v>4.13658107466317</v>
       </c>
       <c r="P8" t="n">
-        <v>359.5680418586018</v>
+        <v>359.553307065536</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25311,28 +25445,28 @@
         <v>0.09089999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2313810634794064</v>
+        <v>0.2311054475100642</v>
       </c>
       <c r="J9" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K9" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1575114655711848</v>
+        <v>0.1588039386277944</v>
       </c>
       <c r="M9" t="n">
-        <v>3.157013676746187</v>
+        <v>3.145415049726741</v>
       </c>
       <c r="N9" t="n">
-        <v>15.69710191106119</v>
+        <v>15.61632460116049</v>
       </c>
       <c r="O9" t="n">
-        <v>3.961956828520623</v>
+        <v>3.951749562049763</v>
       </c>
       <c r="P9" t="n">
-        <v>361.360030275019</v>
+        <v>361.3630613719788</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -25389,28 +25523,28 @@
         <v>0.0915</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1580096125132936</v>
+        <v>0.1567389585804124</v>
       </c>
       <c r="J10" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K10" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L10" t="n">
-        <v>0.08581216526517621</v>
+        <v>0.08548068048323321</v>
       </c>
       <c r="M10" t="n">
-        <v>2.977465102176371</v>
+        <v>2.966234895097764</v>
       </c>
       <c r="N10" t="n">
-        <v>14.58027175834406</v>
+        <v>14.50779228341429</v>
       </c>
       <c r="O10" t="n">
-        <v>3.818412203828191</v>
+        <v>3.808909592444311</v>
       </c>
       <c r="P10" t="n">
-        <v>367.5760252923145</v>
+        <v>367.5899504656383</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -25467,28 +25601,28 @@
         <v>0.0954</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1608870734835558</v>
+        <v>0.161359581244706</v>
       </c>
       <c r="J11" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K11" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L11" t="n">
-        <v>0.08375337360843604</v>
+        <v>0.08517105261338354</v>
       </c>
       <c r="M11" t="n">
-        <v>3.149995105932081</v>
+        <v>3.134721290869807</v>
       </c>
       <c r="N11" t="n">
-        <v>15.5225979288532</v>
+        <v>15.43689326538932</v>
       </c>
       <c r="O11" t="n">
-        <v>3.939872831558552</v>
+        <v>3.928981199419172</v>
       </c>
       <c r="P11" t="n">
-        <v>363.953331989209</v>
+        <v>363.9481570487999</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -25545,28 +25679,28 @@
         <v>0.0953</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1705514592481923</v>
+        <v>0.1681718564107301</v>
       </c>
       <c r="J12" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K12" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L12" t="n">
-        <v>0.09099471740881193</v>
+        <v>0.08958668827644622</v>
       </c>
       <c r="M12" t="n">
-        <v>3.130126409764764</v>
+        <v>3.122530671959526</v>
       </c>
       <c r="N12" t="n">
-        <v>15.92843586144805</v>
+        <v>15.8644220359631</v>
       </c>
       <c r="O12" t="n">
-        <v>3.99104445746324</v>
+        <v>3.983016700437384</v>
       </c>
       <c r="P12" t="n">
-        <v>362.0214225840793</v>
+        <v>362.0474866412468</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -25623,28 +25757,28 @@
         <v>0.0854</v>
       </c>
       <c r="I13" t="n">
-        <v>0.257716005533028</v>
+        <v>0.2518213897348566</v>
       </c>
       <c r="J13" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K13" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1542757702178418</v>
+        <v>0.1489470221399074</v>
       </c>
       <c r="M13" t="n">
-        <v>3.384102581171649</v>
+        <v>3.395430562097832</v>
       </c>
       <c r="N13" t="n">
-        <v>19.9584062356747</v>
+        <v>20.00011555566098</v>
       </c>
       <c r="O13" t="n">
-        <v>4.467483210452468</v>
+        <v>4.472148874496575</v>
       </c>
       <c r="P13" t="n">
-        <v>364.1170678159245</v>
+        <v>364.1816422898402</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -25701,28 +25835,28 @@
         <v>0.0863</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3032411436370522</v>
+        <v>0.2989116614222684</v>
       </c>
       <c r="J14" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K14" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1593807700227899</v>
+        <v>0.1568087243873512</v>
       </c>
       <c r="M14" t="n">
-        <v>3.973876631022874</v>
+        <v>3.970412696240492</v>
       </c>
       <c r="N14" t="n">
-        <v>26.58591899032946</v>
+        <v>26.51942484158489</v>
       </c>
       <c r="O14" t="n">
-        <v>5.15615350725029</v>
+        <v>5.149701432275942</v>
       </c>
       <c r="P14" t="n">
-        <v>366.8017086791268</v>
+        <v>366.8491336964292</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -25779,28 +25913,28 @@
         <v>0.0477</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5260035784249726</v>
+        <v>0.5207791116886138</v>
       </c>
       <c r="J15" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K15" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1922851375392262</v>
+        <v>0.1908427678206397</v>
       </c>
       <c r="M15" t="n">
-        <v>5.793404182581019</v>
+        <v>5.785250544289838</v>
       </c>
       <c r="N15" t="n">
-        <v>63.7091454470192</v>
+        <v>63.47267884795025</v>
       </c>
       <c r="O15" t="n">
-        <v>7.981800889963317</v>
+        <v>7.966974259274989</v>
       </c>
       <c r="P15" t="n">
-        <v>370.1536550574277</v>
+        <v>370.2108837469052</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -25857,28 +25991,28 @@
         <v>0.0274</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.01351474337837109</v>
+        <v>-0.007070439881082022</v>
       </c>
       <c r="J16" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K16" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0001133511429076695</v>
+        <v>3.135338937143572e-05</v>
       </c>
       <c r="M16" t="n">
-        <v>6.703732326194426</v>
+        <v>6.704204170271941</v>
       </c>
       <c r="N16" t="n">
-        <v>88.31866558123293</v>
+        <v>88.00700801327817</v>
       </c>
       <c r="O16" t="n">
-        <v>9.397801103515276</v>
+        <v>9.381205040573315</v>
       </c>
       <c r="P16" t="n">
-        <v>367.2936302883468</v>
+        <v>367.2230396887214</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -25916,7 +26050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q358"/>
+  <dimension ref="A1:Q360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57017,6 +57151,180 @@
         </is>
       </c>
     </row>
+    <row r="359">
+      <c r="A359" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>-36.72368480445776,175.71709621770069</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>-36.72365159452964,175.7179999971911</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>-36.723570611379024,175.71888455290255</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>-36.72340814400588,175.71973877451424</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>-36.723278567433994,175.7206225314805</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>-36.7230783246637,175.72148673534724</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>-36.72287978724542,175.7223514530004</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>-36.72267827677832,175.72321415821762</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>-36.72245773298311,175.724056673772</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>-36.72215780986904,175.7248519951767</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>-36.721827515223886,175.72564844304836</t>
+        </is>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>-36.72142548208753,175.72638554756335</t>
+        </is>
+      </c>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>-36.720942374897035,175.72704271095665</t>
+        </is>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>-36.72043732585811,175.72760373862067</t>
+        </is>
+      </c>
+      <c r="P359" t="inlineStr">
+        <is>
+          <t>-36.7198391228132,175.7280303882345</t>
+        </is>
+      </c>
+      <c r="Q359" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>-36.72368098480883,175.7170954175814</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>-36.723648485517806,175.7179993459078</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>-36.72357563601532,175.7188858666884</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>-36.72341065106396,175.71973968679853</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>-36.723276430994794,175.72062164655824</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>-36.7230806374359,175.7214876706301</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>-36.722899381891146,175.722359100112</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>-36.722696944685374,175.72322136230954</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>-36.722467370815856,175.72406168999737</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>-36.722159058215865,175.72485289012678</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>-36.72182471601609,175.72564619546586</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>-36.72143201726981,175.72639169499203</t>
+        </is>
+      </c>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t>-36.720942374897035,175.72704271095665</t>
+        </is>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>-36.72043732585811,175.72760373862067</t>
+        </is>
+      </c>
+      <c r="P360" t="inlineStr">
+        <is>
+          <t>-36.7198391228132,175.7280303882345</t>
+        </is>
+      </c>
+      <c r="Q360" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0157/nzd0157.xlsx
+++ b/data/nzd0157/nzd0157.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q360"/>
+  <dimension ref="A1:Q362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20957,6 +20957,120 @@
         </is>
       </c>
     </row>
+    <row r="361">
+      <c r="A361" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>392.36</v>
+      </c>
+      <c r="C361" t="n">
+        <v>383.98</v>
+      </c>
+      <c r="D361" t="n">
+        <v>380.13</v>
+      </c>
+      <c r="E361" t="n">
+        <v>381.35</v>
+      </c>
+      <c r="F361" t="n">
+        <v>371.27</v>
+      </c>
+      <c r="G361" t="n">
+        <v>369.46</v>
+      </c>
+      <c r="H361" t="n">
+        <v>367.57</v>
+      </c>
+      <c r="I361" t="n">
+        <v>367.24</v>
+      </c>
+      <c r="J361" t="n">
+        <v>371</v>
+      </c>
+      <c r="K361" t="n">
+        <v>369.28</v>
+      </c>
+      <c r="L361" t="n">
+        <v>365.06</v>
+      </c>
+      <c r="M361" t="n">
+        <v>365.98</v>
+      </c>
+      <c r="N361" t="n">
+        <v>371.47</v>
+      </c>
+      <c r="O361" t="n">
+        <v>380.62</v>
+      </c>
+      <c r="P361" t="n">
+        <v>371.66</v>
+      </c>
+      <c r="Q361" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>392.88</v>
+      </c>
+      <c r="C362" t="n">
+        <v>383.44</v>
+      </c>
+      <c r="D362" t="n">
+        <v>378.55</v>
+      </c>
+      <c r="E362" t="n">
+        <v>378.69</v>
+      </c>
+      <c r="F362" t="n">
+        <v>369.19</v>
+      </c>
+      <c r="G362" t="n">
+        <v>367.69</v>
+      </c>
+      <c r="H362" t="n">
+        <v>364.78</v>
+      </c>
+      <c r="I362" t="n">
+        <v>364.2</v>
+      </c>
+      <c r="J362" t="n">
+        <v>368.68</v>
+      </c>
+      <c r="K362" t="n">
+        <v>367.2</v>
+      </c>
+      <c r="L362" t="n">
+        <v>362.67</v>
+      </c>
+      <c r="M362" t="n">
+        <v>362.99</v>
+      </c>
+      <c r="N362" t="n">
+        <v>368.62</v>
+      </c>
+      <c r="O362" t="n">
+        <v>377.39</v>
+      </c>
+      <c r="P362" t="n">
+        <v>366.63</v>
+      </c>
+      <c r="Q362" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20968,7 +21082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B376"/>
+  <dimension ref="A1:B378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24731,6 +24845,26 @@
       </c>
       <c r="B376" t="n">
         <v>-0.34</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>0.29</v>
       </c>
     </row>
   </sheetData>
@@ -24899,28 +25033,28 @@
         <v>0.0555</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2760193931334979</v>
+        <v>0.2813448622067847</v>
       </c>
       <c r="J2" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K2" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2674724578444523</v>
+        <v>0.2752896835119675</v>
       </c>
       <c r="M2" t="n">
-        <v>2.577435497739846</v>
+        <v>2.589562579481622</v>
       </c>
       <c r="N2" t="n">
-        <v>11.63243887428726</v>
+        <v>11.69637214580664</v>
       </c>
       <c r="O2" t="n">
-        <v>3.410636139239608</v>
+        <v>3.419995927747085</v>
       </c>
       <c r="P2" t="n">
-        <v>380.2926960740504</v>
+        <v>380.2345689389943</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -24977,28 +25111,28 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3909485631847673</v>
+        <v>0.3989231071621324</v>
       </c>
       <c r="J3" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K3" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L3" t="n">
-        <v>0.299778877690698</v>
+        <v>0.3078813152675992</v>
       </c>
       <c r="M3" t="n">
-        <v>3.572055825588657</v>
+        <v>3.590790739996812</v>
       </c>
       <c r="N3" t="n">
-        <v>19.90307211095878</v>
+        <v>20.08049064123862</v>
       </c>
       <c r="O3" t="n">
-        <v>4.461285925712314</v>
+        <v>4.481126046122628</v>
       </c>
       <c r="P3" t="n">
-        <v>365.8556538875935</v>
+        <v>365.7686229411697</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25055,28 +25189,28 @@
         <v>0.1281</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3454323805376072</v>
+        <v>0.3487847827252462</v>
       </c>
       <c r="J4" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K4" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2553701391775827</v>
+        <v>0.2608953650409735</v>
       </c>
       <c r="M4" t="n">
-        <v>3.345343770871169</v>
+        <v>3.343394674689245</v>
       </c>
       <c r="N4" t="n">
-        <v>19.39738215046525</v>
+        <v>19.34431309333952</v>
       </c>
       <c r="O4" t="n">
-        <v>4.404245923023061</v>
+        <v>4.398217035724763</v>
       </c>
       <c r="P4" t="n">
-        <v>366.9300817377563</v>
+        <v>366.8935061785185</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25133,28 +25267,28 @@
         <v>0.09959999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2456864306677493</v>
+        <v>0.2523332144944882</v>
       </c>
       <c r="J5" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K5" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1639753423273679</v>
+        <v>0.1714607906688199</v>
       </c>
       <c r="M5" t="n">
-        <v>3.165878925742411</v>
+        <v>3.181135268800278</v>
       </c>
       <c r="N5" t="n">
-        <v>16.98734017670453</v>
+        <v>17.09977398083464</v>
       </c>
       <c r="O5" t="n">
-        <v>4.121570110613737</v>
+        <v>4.135187296947339</v>
       </c>
       <c r="P5" t="n">
-        <v>367.3623267175452</v>
+        <v>367.2893119659463</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25211,28 +25345,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1515734590669267</v>
+        <v>0.1544785193406722</v>
       </c>
       <c r="J6" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K6" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08149161170638741</v>
+        <v>0.08510373456624287</v>
       </c>
       <c r="M6" t="n">
-        <v>2.886628704795142</v>
+        <v>2.881660023656433</v>
       </c>
       <c r="N6" t="n">
-        <v>14.2935150963031</v>
+        <v>14.25780657786652</v>
       </c>
       <c r="O6" t="n">
-        <v>3.780676539497011</v>
+        <v>3.775951082557415</v>
       </c>
       <c r="P6" t="n">
-        <v>363.4961322217433</v>
+        <v>363.4642277761597</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25289,28 +25423,28 @@
         <v>0.1229</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2276146257326646</v>
+        <v>0.2287087460818339</v>
       </c>
       <c r="J7" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K7" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L7" t="n">
-        <v>0.182348951506448</v>
+        <v>0.1855362421692429</v>
       </c>
       <c r="M7" t="n">
-        <v>2.846245620441249</v>
+        <v>2.834414994543482</v>
       </c>
       <c r="N7" t="n">
-        <v>12.8229384809846</v>
+        <v>12.76150336546206</v>
       </c>
       <c r="O7" t="n">
-        <v>3.580913079227782</v>
+        <v>3.572324644466409</v>
       </c>
       <c r="P7" t="n">
-        <v>361.4220403560958</v>
+        <v>361.4100325861856</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25367,28 +25501,28 @@
         <v>0.074</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2396853756141315</v>
+        <v>0.2398275534728309</v>
       </c>
       <c r="J8" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K8" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1563460267995564</v>
+        <v>0.1580617123748229</v>
       </c>
       <c r="M8" t="n">
-        <v>3.240057250385952</v>
+        <v>3.229761510172953</v>
       </c>
       <c r="N8" t="n">
-        <v>17.11130298726151</v>
+        <v>17.02726980103532</v>
       </c>
       <c r="O8" t="n">
-        <v>4.13658107466317</v>
+        <v>4.126411249625432</v>
       </c>
       <c r="P8" t="n">
-        <v>359.553307065536</v>
+        <v>359.5517678892622</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25445,28 +25579,28 @@
         <v>0.09089999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2311054475100642</v>
+        <v>0.2289936356723803</v>
       </c>
       <c r="J9" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K9" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1588039386277944</v>
+        <v>0.1577307747140207</v>
       </c>
       <c r="M9" t="n">
-        <v>3.145415049726741</v>
+        <v>3.138100939970245</v>
       </c>
       <c r="N9" t="n">
-        <v>15.61632460116049</v>
+        <v>15.56232952873775</v>
       </c>
       <c r="O9" t="n">
-        <v>3.951749562049763</v>
+        <v>3.944911853101125</v>
       </c>
       <c r="P9" t="n">
-        <v>361.3630613719788</v>
+        <v>361.386291789496</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -25523,28 +25657,28 @@
         <v>0.0915</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1567389585804124</v>
+        <v>0.1545255540476342</v>
       </c>
       <c r="J10" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K10" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L10" t="n">
-        <v>0.08548068048323321</v>
+        <v>0.0840795378010003</v>
       </c>
       <c r="M10" t="n">
-        <v>2.966234895097764</v>
+        <v>2.959300998997388</v>
       </c>
       <c r="N10" t="n">
-        <v>14.50779228341429</v>
+        <v>14.45643975954262</v>
       </c>
       <c r="O10" t="n">
-        <v>3.808909592444311</v>
+        <v>3.802162510932775</v>
       </c>
       <c r="P10" t="n">
-        <v>367.5899504656383</v>
+        <v>367.6142911679322</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -25601,28 +25735,28 @@
         <v>0.0954</v>
       </c>
       <c r="I11" t="n">
-        <v>0.161359581244706</v>
+        <v>0.1612695234037451</v>
       </c>
       <c r="J11" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K11" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L11" t="n">
-        <v>0.08517105261338354</v>
+        <v>0.08602399640932845</v>
       </c>
       <c r="M11" t="n">
-        <v>3.134721290869807</v>
+        <v>3.123119712743635</v>
       </c>
       <c r="N11" t="n">
-        <v>15.43689326538932</v>
+        <v>15.35723641181047</v>
       </c>
       <c r="O11" t="n">
-        <v>3.928981199419172</v>
+        <v>3.918831000669775</v>
       </c>
       <c r="P11" t="n">
-        <v>363.9481570487999</v>
+        <v>363.9491638540312</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -25679,28 +25813,28 @@
         <v>0.0953</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1681718564107301</v>
+        <v>0.1651340488437352</v>
       </c>
       <c r="J12" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K12" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L12" t="n">
-        <v>0.08958668827644622</v>
+        <v>0.08739719423188941</v>
       </c>
       <c r="M12" t="n">
-        <v>3.122530671959526</v>
+        <v>3.117671102661421</v>
       </c>
       <c r="N12" t="n">
-        <v>15.8644220359631</v>
+        <v>15.82525999911785</v>
       </c>
       <c r="O12" t="n">
-        <v>3.983016700437384</v>
+        <v>3.978097535143884</v>
       </c>
       <c r="P12" t="n">
-        <v>362.0474866412468</v>
+        <v>362.0808867428759</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -25757,28 +25891,28 @@
         <v>0.0854</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2518213897348566</v>
+        <v>0.2445992005865018</v>
       </c>
       <c r="J13" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K13" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1489470221399074</v>
+        <v>0.1417439225155275</v>
       </c>
       <c r="M13" t="n">
-        <v>3.395430562097832</v>
+        <v>3.415367843316</v>
       </c>
       <c r="N13" t="n">
-        <v>20.00011555566098</v>
+        <v>20.1333384024214</v>
       </c>
       <c r="O13" t="n">
-        <v>4.472148874496575</v>
+        <v>4.487018876985186</v>
       </c>
       <c r="P13" t="n">
-        <v>364.1816422898402</v>
+        <v>364.2610265517979</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -25835,28 +25969,28 @@
         <v>0.0863</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2989116614222684</v>
+        <v>0.2934851114465098</v>
       </c>
       <c r="J14" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K14" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1568087243873512</v>
+        <v>0.1529334589944241</v>
       </c>
       <c r="M14" t="n">
-        <v>3.970412696240492</v>
+        <v>3.971784898075379</v>
       </c>
       <c r="N14" t="n">
-        <v>26.51942484158489</v>
+        <v>26.51431740063871</v>
       </c>
       <c r="O14" t="n">
-        <v>5.149701432275942</v>
+        <v>5.149205511594843</v>
       </c>
       <c r="P14" t="n">
-        <v>366.8491336964292</v>
+        <v>366.9087858134632</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -25913,28 +26047,28 @@
         <v>0.0477</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5207791116886138</v>
+        <v>0.5148945283318291</v>
       </c>
       <c r="J15" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K15" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1908427678206397</v>
+        <v>0.1888457083913876</v>
       </c>
       <c r="M15" t="n">
-        <v>5.785250544289838</v>
+        <v>5.780163824501291</v>
       </c>
       <c r="N15" t="n">
-        <v>63.47267884795025</v>
+        <v>63.28870219212308</v>
       </c>
       <c r="O15" t="n">
-        <v>7.966974259274989</v>
+        <v>7.955419674166981</v>
       </c>
       <c r="P15" t="n">
-        <v>370.2108837469052</v>
+        <v>370.2755721802234</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -25991,28 +26125,28 @@
         <v>0.0274</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.007070439881082022</v>
+        <v>-0.004736363986267068</v>
       </c>
       <c r="J16" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K16" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L16" t="n">
-        <v>3.135338937143572e-05</v>
+        <v>1.423587393223347e-05</v>
       </c>
       <c r="M16" t="n">
-        <v>6.704204170271941</v>
+        <v>6.683014541824606</v>
       </c>
       <c r="N16" t="n">
-        <v>88.00700801327817</v>
+        <v>87.5776143309521</v>
       </c>
       <c r="O16" t="n">
-        <v>9.381205040573315</v>
+        <v>9.358291207851575</v>
       </c>
       <c r="P16" t="n">
-        <v>367.2230396887214</v>
+        <v>367.1974336110792</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -26050,7 +26184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q360"/>
+  <dimension ref="A1:Q362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57325,6 +57459,180 @@
         </is>
       </c>
     </row>
+    <row r="361">
+      <c r="A361" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>-36.72367290136572,175.71709372430593</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>-36.723640935060494,175.71799776422006</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>-36.723570523227515,175.71888452985368</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>-36.72340122798355,175.7197362578682</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>-36.72327514913128,175.7206211156049</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>-36.723075583600334,175.72148562686397</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>-36.72288649067693,175.72235406911705</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>-36.722688686072196,175.72321817524536</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>-36.72246014244131,175.72405792782823</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>-36.722154064828516,175.72484931032656</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>-36.72182191680826,175.72564394788355</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>-36.72142756472809,175.72638750663393</t>
+        </is>
+      </c>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>-36.720940027308394,175.72704009657113</t>
+        </is>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>-36.72043253598312,175.7275952006694</t>
+        </is>
+      </c>
+      <c r="P361" t="inlineStr">
+        <is>
+          <t>-36.71984277549056,175.72804086126362</t>
+        </is>
+      </c>
+      <c r="Q361" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>-36.723668282255346,175.71709275672012</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>-36.72364573182162,175.71799876905695</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>-36.72358445116662,175.71888817157622</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>-36.723424223757476,175.71974462571816</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>-36.72329292430509,175.7206284781595</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>-36.72309074510687,175.7214917581632</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>-36.72291046833513,175.72236342676905</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>-36.72271483834685,175.7232282676178</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>-36.72247941810638,175.7240679602809</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>-36.72217029333694,175.72486094467902</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>-36.72183999817693,175.72565846605337</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>-36.72144903746811,175.72640770533323</t>
+        </is>
+      </c>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>-36.72095914338541,175.72706138514357</t>
+        </is>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>-36.72044917178273,175.72762485398852</t>
+        </is>
+      </c>
+      <c r="P362" t="inlineStr">
+        <is>
+          <t>-36.71986078818936,175.72809250768574</t>
+        </is>
+      </c>
+      <c r="Q362" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0157/nzd0157.xlsx
+++ b/data/nzd0157/nzd0157.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q362"/>
+  <dimension ref="A1:Q363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21071,6 +21071,63 @@
         </is>
       </c>
     </row>
+    <row r="363">
+      <c r="A363" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>393.37</v>
+      </c>
+      <c r="C363" t="n">
+        <v>383.56</v>
+      </c>
+      <c r="D363" t="n">
+        <v>379.48</v>
+      </c>
+      <c r="E363" t="n">
+        <v>379.3</v>
+      </c>
+      <c r="F363" t="n">
+        <v>369.12</v>
+      </c>
+      <c r="G363" t="n">
+        <v>368.26</v>
+      </c>
+      <c r="H363" t="n">
+        <v>365.01</v>
+      </c>
+      <c r="I363" t="n">
+        <v>364.13</v>
+      </c>
+      <c r="J363" t="n">
+        <v>368.94</v>
+      </c>
+      <c r="K363" t="n">
+        <v>367.26</v>
+      </c>
+      <c r="L363" t="n">
+        <v>363.32</v>
+      </c>
+      <c r="M363" t="n">
+        <v>363.82</v>
+      </c>
+      <c r="N363" t="n">
+        <v>368.67</v>
+      </c>
+      <c r="O363" t="n">
+        <v>377.81</v>
+      </c>
+      <c r="P363" t="n">
+        <v>365.71</v>
+      </c>
+      <c r="Q363" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21082,7 +21139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B378"/>
+  <dimension ref="A1:B379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24865,6 +24922,16 @@
       </c>
       <c r="B378" t="n">
         <v>0.29</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>0.82</v>
       </c>
     </row>
   </sheetData>
@@ -25033,28 +25100,28 @@
         <v>0.0555</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2813448622067847</v>
+        <v>0.2843563505364229</v>
       </c>
       <c r="J2" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K2" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2752896835119675</v>
+        <v>0.2793734419189989</v>
       </c>
       <c r="M2" t="n">
-        <v>2.589562579481622</v>
+        <v>2.597519017741064</v>
       </c>
       <c r="N2" t="n">
-        <v>11.69637214580664</v>
+        <v>11.7468230797956</v>
       </c>
       <c r="O2" t="n">
-        <v>3.419995927747085</v>
+        <v>3.427363867434504</v>
       </c>
       <c r="P2" t="n">
-        <v>380.2345689389943</v>
+        <v>380.2015970026198</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25111,28 +25178,28 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3989231071621324</v>
+        <v>0.4027357137060656</v>
       </c>
       <c r="J3" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K3" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3078813152675992</v>
+        <v>0.3118533280685335</v>
       </c>
       <c r="M3" t="n">
-        <v>3.590790739996812</v>
+        <v>3.599274267883006</v>
       </c>
       <c r="N3" t="n">
-        <v>20.08049064123862</v>
+        <v>20.1576702661796</v>
       </c>
       <c r="O3" t="n">
-        <v>4.481126046122628</v>
+        <v>4.489729420152131</v>
       </c>
       <c r="P3" t="n">
-        <v>365.7686229411697</v>
+        <v>365.7268797874108</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25189,28 +25256,28 @@
         <v>0.1281</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3487847827252462</v>
+        <v>0.3504927120486346</v>
       </c>
       <c r="J4" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K4" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2608953650409735</v>
+        <v>0.2637095013599492</v>
       </c>
       <c r="M4" t="n">
-        <v>3.343394674689245</v>
+        <v>3.342522260001471</v>
       </c>
       <c r="N4" t="n">
-        <v>19.34431309333952</v>
+        <v>19.31749557792788</v>
       </c>
       <c r="O4" t="n">
-        <v>4.398217035724763</v>
+        <v>4.395167298059071</v>
       </c>
       <c r="P4" t="n">
-        <v>366.8935061785185</v>
+        <v>366.8748065420535</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25267,28 +25334,28 @@
         <v>0.09959999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2523332144944882</v>
+        <v>0.2551809640654753</v>
       </c>
       <c r="J5" t="n">
+        <v>362</v>
+      </c>
+      <c r="K5" t="n">
         <v>361</v>
       </c>
-      <c r="K5" t="n">
-        <v>360</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.1714607906688199</v>
+        <v>0.174949033393518</v>
       </c>
       <c r="M5" t="n">
-        <v>3.181135268800278</v>
+        <v>3.186548159158122</v>
       </c>
       <c r="N5" t="n">
-        <v>17.09977398083464</v>
+        <v>17.12533710448694</v>
       </c>
       <c r="O5" t="n">
-        <v>4.135187296947339</v>
+        <v>4.138277069564935</v>
       </c>
       <c r="P5" t="n">
-        <v>367.2893119659463</v>
+        <v>367.2579218714149</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25345,28 +25412,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1544785193406722</v>
+        <v>0.1552871589004766</v>
       </c>
       <c r="J6" t="n">
+        <v>362</v>
+      </c>
+      <c r="K6" t="n">
         <v>361</v>
       </c>
-      <c r="K6" t="n">
-        <v>360</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.08510373456624287</v>
+        <v>0.08637441018513325</v>
       </c>
       <c r="M6" t="n">
-        <v>2.881660023656433</v>
+        <v>2.876728125827104</v>
       </c>
       <c r="N6" t="n">
-        <v>14.25780657786652</v>
+        <v>14.22419182033428</v>
       </c>
       <c r="O6" t="n">
-        <v>3.775951082557415</v>
+        <v>3.771497291571914</v>
       </c>
       <c r="P6" t="n">
-        <v>363.4642277761597</v>
+        <v>363.4553143265774</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25423,28 +25490,28 @@
         <v>0.1229</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2287087460818339</v>
+        <v>0.2290596089604342</v>
       </c>
       <c r="J7" t="n">
+        <v>362</v>
+      </c>
+      <c r="K7" t="n">
         <v>361</v>
       </c>
-      <c r="K7" t="n">
-        <v>360</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.1855362421692429</v>
+        <v>0.1869245389298729</v>
       </c>
       <c r="M7" t="n">
-        <v>2.834414994543482</v>
+        <v>2.827822064773446</v>
       </c>
       <c r="N7" t="n">
-        <v>12.76150336546206</v>
+        <v>12.72726003065243</v>
       </c>
       <c r="O7" t="n">
-        <v>3.572324644466409</v>
+        <v>3.567528560593795</v>
       </c>
       <c r="P7" t="n">
-        <v>361.4100325861856</v>
+        <v>361.4061651046349</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25501,28 +25568,28 @@
         <v>0.074</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2398275534728309</v>
+        <v>0.2392419911241829</v>
       </c>
       <c r="J8" t="n">
+        <v>362</v>
+      </c>
+      <c r="K8" t="n">
         <v>361</v>
       </c>
-      <c r="K8" t="n">
-        <v>360</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.1580617123748229</v>
+        <v>0.1582096389618969</v>
       </c>
       <c r="M8" t="n">
-        <v>3.229761510172953</v>
+        <v>3.224084212300508</v>
       </c>
       <c r="N8" t="n">
-        <v>17.02726980103532</v>
+        <v>16.98318642272442</v>
       </c>
       <c r="O8" t="n">
-        <v>4.126411249625432</v>
+        <v>4.12106617548474</v>
       </c>
       <c r="P8" t="n">
-        <v>359.5517678892622</v>
+        <v>359.5582224095843</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25579,28 +25646,28 @@
         <v>0.09089999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2289936356723803</v>
+        <v>0.227073276863261</v>
       </c>
       <c r="J9" t="n">
+        <v>362</v>
+      </c>
+      <c r="K9" t="n">
         <v>361</v>
       </c>
-      <c r="K9" t="n">
-        <v>360</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.1577307747140207</v>
+        <v>0.156038280050432</v>
       </c>
       <c r="M9" t="n">
-        <v>3.138100939970245</v>
+        <v>3.138579151249959</v>
       </c>
       <c r="N9" t="n">
-        <v>15.56232952873775</v>
+        <v>15.55238503711901</v>
       </c>
       <c r="O9" t="n">
-        <v>3.944911853101125</v>
+        <v>3.943651231678457</v>
       </c>
       <c r="P9" t="n">
-        <v>361.386291789496</v>
+        <v>361.4074594670076</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -25657,28 +25724,28 @@
         <v>0.0915</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1545255540476342</v>
+        <v>0.1529416572021687</v>
       </c>
       <c r="J10" t="n">
+        <v>362</v>
+      </c>
+      <c r="K10" t="n">
         <v>361</v>
       </c>
-      <c r="K10" t="n">
-        <v>360</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.0840795378010003</v>
+        <v>0.08285647692172204</v>
       </c>
       <c r="M10" t="n">
-        <v>2.959300998997388</v>
+        <v>2.958007096794368</v>
       </c>
       <c r="N10" t="n">
-        <v>14.45643975954262</v>
+        <v>14.43895540372296</v>
       </c>
       <c r="O10" t="n">
-        <v>3.802162510932775</v>
+        <v>3.799862550635609</v>
       </c>
       <c r="P10" t="n">
-        <v>367.6142911679322</v>
+        <v>367.6317501018968</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -25735,28 +25802,28 @@
         <v>0.0954</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1612695234037451</v>
+        <v>0.1606787915229441</v>
       </c>
       <c r="J11" t="n">
+        <v>362</v>
+      </c>
+      <c r="K11" t="n">
         <v>361</v>
       </c>
-      <c r="K11" t="n">
-        <v>360</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.08602399640932845</v>
+        <v>0.08591693455804572</v>
       </c>
       <c r="M11" t="n">
-        <v>3.123119712743635</v>
+        <v>3.117445973416397</v>
       </c>
       <c r="N11" t="n">
-        <v>15.35723641181047</v>
+        <v>15.31783385066369</v>
       </c>
       <c r="O11" t="n">
-        <v>3.918831000669775</v>
+        <v>3.913800435722763</v>
       </c>
       <c r="P11" t="n">
-        <v>363.9491638540312</v>
+        <v>363.9556753569281</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -25813,28 +25880,28 @@
         <v>0.0953</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1651340488437352</v>
+        <v>0.1633388162950553</v>
       </c>
       <c r="J12" t="n">
+        <v>362</v>
+      </c>
+      <c r="K12" t="n">
         <v>361</v>
       </c>
-      <c r="K12" t="n">
-        <v>360</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.08739719423188941</v>
+        <v>0.08601029500845825</v>
       </c>
       <c r="M12" t="n">
-        <v>3.117671102661421</v>
+        <v>3.116347843714647</v>
       </c>
       <c r="N12" t="n">
-        <v>15.82525999911785</v>
+        <v>15.81040612650803</v>
       </c>
       <c r="O12" t="n">
-        <v>3.978097535143884</v>
+        <v>3.976230140033149</v>
       </c>
       <c r="P12" t="n">
-        <v>362.0808867428759</v>
+        <v>362.1006751821345</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -25891,28 +25958,28 @@
         <v>0.0854</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2445992005865018</v>
+        <v>0.24068564826473</v>
       </c>
       <c r="J13" t="n">
+        <v>362</v>
+      </c>
+      <c r="K13" t="n">
         <v>361</v>
       </c>
-      <c r="K13" t="n">
-        <v>360</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.1417439225155275</v>
+        <v>0.1377869397110917</v>
       </c>
       <c r="M13" t="n">
-        <v>3.415367843316</v>
+        <v>3.427061263934563</v>
       </c>
       <c r="N13" t="n">
-        <v>20.1333384024214</v>
+        <v>20.21530430673809</v>
       </c>
       <c r="O13" t="n">
-        <v>4.487018876985186</v>
+        <v>4.496143270263759</v>
       </c>
       <c r="P13" t="n">
-        <v>364.2610265517979</v>
+        <v>364.3041647471595</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -25969,28 +26036,28 @@
         <v>0.0863</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2934851114465098</v>
+        <v>0.2900562091931412</v>
       </c>
       <c r="J14" t="n">
+        <v>362</v>
+      </c>
+      <c r="K14" t="n">
         <v>361</v>
       </c>
-      <c r="K14" t="n">
-        <v>360</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.1529334589944241</v>
+        <v>0.1501927949130923</v>
       </c>
       <c r="M14" t="n">
-        <v>3.971784898075379</v>
+        <v>3.975445946855226</v>
       </c>
       <c r="N14" t="n">
-        <v>26.51431740063871</v>
+        <v>26.54660542457444</v>
       </c>
       <c r="O14" t="n">
-        <v>5.149205511594843</v>
+        <v>5.152339800961737</v>
       </c>
       <c r="P14" t="n">
-        <v>366.9087858134632</v>
+        <v>366.9465818215703</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -26047,28 +26114,28 @@
         <v>0.0477</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5148945283318291</v>
+        <v>0.5113336286402418</v>
       </c>
       <c r="J15" t="n">
+        <v>362</v>
+      </c>
+      <c r="K15" t="n">
         <v>361</v>
       </c>
-      <c r="K15" t="n">
-        <v>360</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.1888457083913876</v>
+        <v>0.1873943327407769</v>
       </c>
       <c r="M15" t="n">
-        <v>5.780163824501291</v>
+        <v>5.780419382933583</v>
       </c>
       <c r="N15" t="n">
-        <v>63.28870219212308</v>
+        <v>63.2274194461173</v>
       </c>
       <c r="O15" t="n">
-        <v>7.955419674166981</v>
+        <v>7.951567106307869</v>
       </c>
       <c r="P15" t="n">
-        <v>370.2755721802234</v>
+        <v>370.3148231660103</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -26125,28 +26192,28 @@
         <v>0.0274</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.004736363986267068</v>
+        <v>-0.00548554689713926</v>
       </c>
       <c r="J16" t="n">
+        <v>362</v>
+      </c>
+      <c r="K16" t="n">
         <v>361</v>
       </c>
-      <c r="K16" t="n">
-        <v>360</v>
-      </c>
       <c r="L16" t="n">
-        <v>1.423587393223347e-05</v>
+        <v>1.921283100492222e-05</v>
       </c>
       <c r="M16" t="n">
-        <v>6.683014541824606</v>
+        <v>6.667555896407674</v>
       </c>
       <c r="N16" t="n">
-        <v>87.5776143309521</v>
+        <v>87.34006464839842</v>
       </c>
       <c r="O16" t="n">
-        <v>9.358291207851575</v>
+        <v>9.345590652730218</v>
       </c>
       <c r="P16" t="n">
-        <v>367.1974336110792</v>
+        <v>367.2056916835703</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -26184,7 +26251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q362"/>
+  <dimension ref="A1:Q363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57633,6 +57700,93 @@
         </is>
       </c>
     </row>
+    <row r="363">
+      <c r="A363" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>-36.72366392963211,175.7170918449567</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>-36.72364466587471,175.71799854575983</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>-36.723576253075905,175.7188860280305</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>-36.72341895029059,175.71974270677464</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>-36.72329352250805,175.72062872593784</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>-36.72308586258788,175.72148978367673</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>-36.72290849168235,175.72236265534949</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>-36.72271544053737,175.72322850000805</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>-36.72247725790259,175.72406683595406</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>-36.72216982520692,175.72486060907264</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>-36.72183508065009,175.72565451759644</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>-36.721443076808235,175.72640209833529</t>
+        </is>
+      </c>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>-36.72095880801567,175.72706101165974</t>
+        </is>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>-36.7204470086142,175.72762099813826</t>
+        </is>
+      </c>
+      <c r="P363" t="inlineStr">
+        <is>
+          <t>-36.71986408275598,175.72810195395232</t>
+        </is>
+      </c>
+      <c r="Q363" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
